--- a/Classeur1.xlsx
+++ b/Classeur1.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\meyns\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Lucas\Code\Java\gestion-des-stocks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{905DF26D-2858-464C-9DA0-D3CD3A923C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E81B91-D68E-4C35-A8D8-44FCEFA899E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="16410" windowHeight="14145" xr2:uid="{3762BBFD-9422-4282-8BA6-BAA7AA462C8D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{3762BBFD-9422-4282-8BA6-BAA7AA462C8D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Organisation Projet" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
   <si>
     <t>Tâches</t>
   </si>
@@ -83,7 +83,28 @@
     <t>Deadline</t>
   </si>
   <si>
-    <t>Faire l'api</t>
+    <t>Faire constructeurs</t>
+  </si>
+  <si>
+    <t>Faire services</t>
+  </si>
+  <si>
+    <t>Faire controller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Structure projet </t>
+  </si>
+  <si>
+    <t>Lucas</t>
+  </si>
+  <si>
+    <t>Yoann Tom Lilian</t>
+  </si>
+  <si>
+    <t>Yoann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diagramme de classe </t>
   </si>
 </sst>
 </file>
@@ -107,7 +128,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -130,24 +151,14 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -482,14 +493,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8C5A2A8-20E9-46C8-AB08-643C75E2D7A3}">
-  <dimension ref="B2:E25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:E27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="3" width="22.88671875" customWidth="1"/>
-    <col min="4" max="4" width="23.21875" customWidth="1"/>
+    <col min="2" max="2" width="31.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="18.86328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -499,11 +511,11 @@
       <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
@@ -513,11 +525,11 @@
       <c r="D3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>45912</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
@@ -527,11 +539,11 @@
       <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>45912</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
@@ -541,11 +553,11 @@
       <c r="D5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>45912</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
@@ -555,11 +567,11 @@
       <c r="D6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>45912</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
         <v>12</v>
       </c>
@@ -569,11 +581,11 @@
       <c r="D7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>45912</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
@@ -583,11 +595,11 @@
       <c r="D8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <v>45912</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
@@ -597,89 +609,134 @@
       <c r="D9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <v>45930</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="2">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="2">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="2">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E18" s="1"/>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E19" s="1"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E20" s="1"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E21" s="1"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E22" s="1"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E23" s="1"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="E24" s="1"/>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B27" t="s">
+        <v>22</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Classeur1.xlsx
+++ b/Classeur1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Lucas\Code\Java\gestion-des-stocks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E81B91-D68E-4C35-A8D8-44FCEFA899E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C60A89F-BD19-4E85-B1CE-897E1F061D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{3762BBFD-9422-4282-8BA6-BAA7AA462C8D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
   <si>
     <t>Tâches</t>
   </si>
@@ -102,9 +102,6 @@
   </si>
   <si>
     <t>Yoann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diagramme de classe </t>
   </si>
 </sst>
 </file>
@@ -493,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8C5A2A8-20E9-46C8-AB08-643C75E2D7A3}">
-  <dimension ref="B2:E27"/>
+  <dimension ref="B2:E25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="31.1328125" bestFit="1" customWidth="1"/>
@@ -733,11 +730,6 @@
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B27" t="s">
-        <v>22</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
